--- a/main/StructureDefinition-bc-patient-by-example.xlsx
+++ b/main/StructureDefinition-bc-patient-by-example.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5517,7 +5517,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>276</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>341</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>390</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>399</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>418</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>421</v>
       </c>
@@ -13180,12 +13180,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO91">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
